--- a/sample_data/wedstrijd-data-2026-10-03.xlsx
+++ b/sample_data/wedstrijd-data-2026-10-03.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -647,13 +647,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -677,10 +677,10 @@
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -696,19 +696,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -745,13 +745,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -794,10 +794,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -843,13 +843,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -968,10 +968,10 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -988,19 +988,19 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -1015,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,10 +1183,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>260.535528</v>
+        <v>239.663682</v>
       </c>
       <c r="D7" t="n">
-        <v>218.852122</v>
+        <v>184.437029</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>248.543089</v>
+        <v>236.551348</v>
       </c>
       <c r="D10" t="n">
-        <v>204.094619</v>
+        <v>186.435694</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>304.913938</v>
+        <v>313.832971</v>
       </c>
       <c r="D13" t="n">
-        <v>199.11516</v>
+        <v>184.134563</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>310.776382</v>
+        <v>348.970537</v>
       </c>
       <c r="D15" t="n">
-        <v>245.033427</v>
+        <v>243.940432</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>272.192771</v>
+        <v>256.423174</v>
       </c>
       <c r="D20" t="n">
-        <v>229.88067</v>
+        <v>177.002941</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>215.099324</v>
+        <v>209.061044</v>
       </c>
       <c r="D25" t="n">
-        <v>224.279758</v>
+        <v>222.160994</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>217.69116</v>
+        <v>207.449388</v>
       </c>
       <c r="D28" t="n">
-        <v>230.12173</v>
+        <v>227.379784</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>244.931165</v>
+        <v>206.053685</v>
       </c>
       <c r="D36" t="n">
-        <v>251.547473</v>
+        <v>258.27275</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>316.321754</v>
+        <v>333.685045</v>
       </c>
       <c r="D37" t="n">
-        <v>276.79543</v>
+        <v>290.393757</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1834,98 +1834,35 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>276.86101</v>
+        <v>276.745999</v>
       </c>
       <c r="D38" t="n">
-        <v>285.39818</v>
+        <v>317.999552</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Speler D</t>
+          <t>Speler E</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>366.627743</v>
+        <v>294.004481</v>
       </c>
       <c r="D39" t="n">
-        <v>179.393458</v>
+        <v>315.963188</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nee</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Speler D</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>331.055325</v>
-      </c>
-      <c r="D40" t="n">
-        <v>141.282784</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Speler B</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" t="n">
-        <v>345.437469</v>
-      </c>
-      <c r="D41" t="n">
-        <v>236.70744</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Nee</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Speler F</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="n">
-        <v>289.438776</v>
-      </c>
-      <c r="D42" t="n">
-        <v>149.377139</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3068,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
@@ -3145,11 +3082,11 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3100,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3181,11 +3118,11 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3136,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3221,7 +3158,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
@@ -3235,11 +3172,11 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
@@ -3253,11 +3190,11 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3307,7 +3244,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3326,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3344,6 +3281,39 @@
         <is>
           <t>Nummer_In</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3357,7 +3327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5646,7 +5616,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Doelpunt</t>
+          <t>Gemist</t>
         </is>
       </c>
     </row>
@@ -5656,14 +5626,10 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Assist</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Speler H</t>
-        </is>
-      </c>
+          <t>0 Kans (tegenstander)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -5672,10 +5638,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kans tegenstander</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>Steal</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Speler D</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
@@ -5684,14 +5654,10 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tegengoal</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Speler D</t>
-        </is>
-      </c>
+          <t>0 Kans (ons)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
@@ -5700,19 +5666,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Schot (veld)</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Speler D</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Gemist</t>
-        </is>
-      </c>
+          <t>0 Kans (tegenstander)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5732,10 +5690,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Kans tegenstander</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+          <t>Rebound</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Speler E</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
@@ -5744,14 +5706,10 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Tegengoal</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Speler H</t>
-        </is>
-      </c>
+          <t>Kans tegenstander</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -5760,7 +5718,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0 Kans (tegenstander)</t>
+          <t>Kans tegenstander</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -5772,12 +5730,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Steal</t>
+          <t>Tegengoal</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Speler F</t>
+          <t>Speler H</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -5788,7 +5746,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Kans tegenstander</t>
+          <t>0 Kans (tegenstander)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -5800,12 +5758,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tegengoal</t>
+          <t>Steal</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Speler G</t>
+          <t>Speler F</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -5816,7 +5774,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0 Kans (tegenstander)</t>
+          <t>Kans tegenstander</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -5828,12 +5786,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Steal</t>
+          <t>Tegengoal</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Speler B</t>
+          <t>Speler G</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -5844,7 +5802,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kans tegenstander</t>
+          <t>0 Kans (ons)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -5856,15 +5814,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tegengoal</t>
+          <t>Schot (veld)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Speler G</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Speler E</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Doelpunt</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5872,139 +5834,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Kans tegenstander</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>Assist</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Speler B</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Tegengoal</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Speler E</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Schot (veld)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Speler D</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Gemist</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Schot (veld)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Speler B</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Gemist</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Rebound</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Speler E</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Schot (veld)</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Speler F</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Gemist</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Rebound</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Speler H</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Vrijworp</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Speler C</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Doelpunt</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sample_data/wedstrijd-data-2026-10-03.xlsx
+++ b/sample_data/wedstrijd-data-2026-10-03.xlsx
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.409868</v>
+        <v>74.607151</v>
       </c>
       <c r="D2" t="n">
-        <v>267.455433</v>
+        <v>301.024942</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>152.277288</v>
+        <v>171.07359</v>
       </c>
       <c r="D3" t="n">
-        <v>114.301424</v>
+        <v>128.647898</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>109.754531</v>
+        <v>123.302049</v>
       </c>
       <c r="D4" t="n">
-        <v>304.115974</v>
+        <v>342.286909</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>113.834872</v>
+        <v>127.886046</v>
       </c>
       <c r="D5" t="n">
-        <v>268.380425</v>
+        <v>302.066034</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>379.109003</v>
+        <v>425.904211</v>
       </c>
       <c r="D6" t="n">
-        <v>264.006981</v>
+        <v>297.14366</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>239.663682</v>
+        <v>269.246498</v>
       </c>
       <c r="D7" t="n">
-        <v>184.437029</v>
+        <v>207.586533</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>132.857714</v>
+        <v>149.256967</v>
       </c>
       <c r="D8" t="n">
-        <v>268.080278</v>
+        <v>301.728214</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>463.140805</v>
+        <v>520.308454</v>
       </c>
       <c r="D9" t="n">
-        <v>190.338714</v>
+        <v>214.228964</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>236.551348</v>
+        <v>265.749994</v>
       </c>
       <c r="D10" t="n">
-        <v>186.435694</v>
+        <v>209.836059</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>193.865444</v>
+        <v>217.795167</v>
       </c>
       <c r="D11" t="n">
-        <v>278.259128</v>
+        <v>313.184656</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>166.701774</v>
+        <v>187.278559</v>
       </c>
       <c r="D12" t="n">
-        <v>247.233994</v>
+        <v>278.265422</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>313.832971</v>
+        <v>352.570851</v>
       </c>
       <c r="D13" t="n">
-        <v>184.134563</v>
+        <v>207.246103</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>380.37282</v>
+        <v>427.324026</v>
       </c>
       <c r="D14" t="n">
-        <v>129.531892</v>
+        <v>145.79001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>348.970537</v>
+        <v>392.045612</v>
       </c>
       <c r="D15" t="n">
-        <v>243.940432</v>
+        <v>274.558469</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>473.72993</v>
+        <v>532.204644</v>
       </c>
       <c r="D16" t="n">
-        <v>159.815733</v>
+        <v>179.874909</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>478.261591</v>
+        <v>537.295669</v>
       </c>
       <c r="D17" t="n">
-        <v>286.975571</v>
+        <v>322.995139</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>412.051479</v>
+        <v>462.912932</v>
       </c>
       <c r="D18" t="n">
-        <v>226.095322</v>
+        <v>254.473542</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>395.439518</v>
+        <v>444.250478</v>
       </c>
       <c r="D19" t="n">
-        <v>274.109738</v>
+        <v>308.514458</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>256.423174</v>
+        <v>288.074692</v>
       </c>
       <c r="D20" t="n">
-        <v>177.002941</v>
+        <v>199.219359</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>81.487763</v>
+        <v>91.546181</v>
       </c>
       <c r="D21" t="n">
-        <v>239.399421</v>
+        <v>269.447496</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>106.603942</v>
+        <v>119.762568</v>
       </c>
       <c r="D22" t="n">
-        <v>274.842984</v>
+        <v>309.339737</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>392.451391</v>
+        <v>440.893512</v>
       </c>
       <c r="D23" t="n">
-        <v>158.296705</v>
+        <v>178.165221</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>332.310362</v>
+        <v>373.328994</v>
       </c>
       <c r="D24" t="n">
-        <v>303.894386</v>
+        <v>342.037509</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>209.061044</v>
+        <v>234.866432</v>
       </c>
       <c r="D25" t="n">
-        <v>222.160994</v>
+        <v>250.045399</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>370.359629</v>
+        <v>416.074861</v>
       </c>
       <c r="D26" t="n">
-        <v>133.683545</v>
+        <v>150.462756</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>380.719301</v>
+        <v>427.713275</v>
       </c>
       <c r="D27" t="n">
-        <v>276.162972</v>
+        <v>310.825403</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>207.449388</v>
+        <v>233.055843</v>
       </c>
       <c r="D28" t="n">
-        <v>227.379784</v>
+        <v>255.919222</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>480.877186</v>
+        <v>540.23412</v>
       </c>
       <c r="D29" t="n">
-        <v>259.305659</v>
+        <v>291.852254</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>199.210251</v>
+        <v>223.799709</v>
       </c>
       <c r="D30" t="n">
-        <v>231.098645</v>
+        <v>260.104854</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>405.929116</v>
+        <v>456.034856</v>
       </c>
       <c r="D31" t="n">
-        <v>130.504577</v>
+        <v>146.884781</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>394.645426</v>
+        <v>443.358368</v>
       </c>
       <c r="D32" t="n">
-        <v>211.299343</v>
+        <v>237.820454</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>140.320368</v>
+        <v>157.640771</v>
       </c>
       <c r="D33" t="n">
-        <v>334.471324</v>
+        <v>376.452293</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>431.669346</v>
+        <v>484.952324</v>
       </c>
       <c r="D34" t="n">
-        <v>157.817188</v>
+        <v>177.625518</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>91.36720200000001</v>
+        <v>102.645085</v>
       </c>
       <c r="D35" t="n">
-        <v>313.466169</v>
+        <v>352.810688</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>206.053685</v>
+        <v>231.487861</v>
       </c>
       <c r="D36" t="n">
-        <v>258.27275</v>
+        <v>290.6897</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>333.685045</v>
+        <v>374.87336</v>
       </c>
       <c r="D37" t="n">
-        <v>290.393757</v>
+        <v>326.842356</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>276.745999</v>
+        <v>310.906059</v>
       </c>
       <c r="D38" t="n">
-        <v>317.999552</v>
+        <v>357.913076</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>294.004481</v>
+        <v>330.294838</v>
       </c>
       <c r="D39" t="n">
-        <v>315.963188</v>
+        <v>355.621118</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
